--- a/su25larvae1.xlsx
+++ b/su25larvae1.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C948202-23CC-44E7-AC2F-5611BDA2B470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EADDCF18-FB8E-4131-A739-8F65867AA3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1671D3F5-3258-4FCD-A730-7B2EEB18175F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="su25larvae1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -68,9 +68,6 @@
     <t>C-MBB-2</t>
   </si>
   <si>
-    <t>na</t>
-  </si>
-  <si>
     <t>C-MBB-4</t>
   </si>
   <si>
@@ -96,6 +93,9 @@
   </si>
   <si>
     <t>MP-Pf-5</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -511,7 +511,7 @@
         <v>45862</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -551,7 +551,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -577,7 +577,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -609,7 +609,7 @@
         <v>45865</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>29</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -632,7 +632,7 @@
         <v>45865</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -649,7 +649,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -658,7 +658,7 @@
         <v>45867</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F8">
         <v>31</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -681,7 +681,7 @@
         <v>45884</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -724,7 +724,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
         <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -796,7 +796,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -805,7 +805,7 @@
         <v>45878</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -814,15 +814,15 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -831,7 +831,7 @@
         <v>45870</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F15">
         <v>20</v>
@@ -840,15 +840,15 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -857,7 +857,7 @@
         <v>45872</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F16">
         <v>11</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -875,11 +875,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1116,20 +1117,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAE018D7-76E4-4339-A516-1CB5FF9FF351}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FBBFF5E-1C5C-4F11-A164-713B6FFE995C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1154,9 +1152,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FBBFF5E-1C5C-4F11-A164-713B6FFE995C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAE018D7-76E4-4339-A516-1CB5FF9FF351}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
